--- a/quizzes/014_self_esteem_multiple_choice_quiz--quizzes.xlsx
+++ b/quizzes/014_self_esteem_multiple_choice_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_confident_at_all'}</t>
+          <t>not_confident_at_all</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not confident at all'}</t>
+          <t>Not confident at all</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_confident'}</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat confident'}</t>
+          <t>Somewhat confident</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_confident'}</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat confident'}</t>
+          <t>Very confident</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_confident'}</t>
+          <t>extremely_confident</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very confident'}</t>
+          <t>Extremely confident</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>feeling_confident_in_general_choices</t>
+          <t>self_description_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_confident'}</t>
+          <t>i_am_a_very_confident_person</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely confident'}</t>
+          <t>I am a very confident person</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_confident_person'}</t>
+          <t>i_am_a_somewhat_confident_person</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very confident person'}</t>
+          <t>I am a somewhat confident person</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_confident_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat confident person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_uncertain_person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat uncertain person</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_uncertain_person'}</t>
+          <t>i_am_an_uncertain_person</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat uncertain person'}</t>
+          <t>I am an uncertain person</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>self_description_choices</t>
+          <t>self_description_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_an_uncertain_person'}</t>
+          <t>i_am_a_very_self-assured_person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'I am an uncertain person'}</t>
+          <t>I am a very self-assured person</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_self-assured_person'}</t>
+          <t>i_am_a_somewhat_self-assured_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very self-assured person'}</t>
+          <t>I am a somewhat self-assured person</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_self-assured_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat self-assured person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_uncertain_person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat uncertain person</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_uncertain_person'}</t>
+          <t>i_am_an_uncertain_person</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat uncertain person'}</t>
+          <t>I am an uncertain person</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>self_description_2_choices</t>
+          <t>self_perception_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_an_uncertain_person'}</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'I am an uncertain person'}</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'old'}</t>
+          <t>somewhat_old</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Old'}</t>
+          <t>Somewhat old</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_old'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat old'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_young</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat young</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_young'}</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat young'}</t>
+          <t>Young</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>self_perception_choices</t>
+          <t>self_description_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'young'}</t>
+          <t>very_young</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Young'}</t>
+          <t>Very young</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'very_young'}</t>
+          <t>somewhat_young</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Very young'}</t>
+          <t>Somewhat young</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_young'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat young'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_old</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat old</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_old'}</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat old'}</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>self_description_3_choices</t>
+          <t>emotional_resilience_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'old'}</t>
+          <t>very_resilient</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Old'}</t>
+          <t>Very resilient</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'very_resilient'}</t>
+          <t>somewhat_resilient</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Very resilient'}</t>
+          <t>Somewhat resilient</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_resilient'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat resilient'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_fragile</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat fragile</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_fragile'}</t>
+          <t>fragile</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat fragile'}</t>
+          <t>Fragile</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>emotional_resilience_choices</t>
+          <t>emotional_resilience_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'fragile'}</t>
+          <t>i_have_very_high_emotional_resilience</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Fragile'}</t>
+          <t>I have very high emotional resilience</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_very_high_emotional_resilience'}</t>
+          <t>i_have_somewhat_high_emotional_resilience</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'I have very high emotional resilience'}</t>
+          <t>I have somewhat high emotional resilience</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_somewhat_high_emotional_resilience'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'I have somewhat high emotional resilience'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>i_have_somewhat_low_emotional_resilience</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>I have somewhat low emotional resilience</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_somewhat_low_emotional_resilience'}</t>
+          <t>i_have_very_low_emotional_resilience</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'I have somewhat low emotional resilience'}</t>
+          <t>I have very low emotional resilience</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>emotional_resilience_2_choices</t>
+          <t>self_worth_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_very_low_emotional_resilience'}</t>
+          <t>i_am_very_valuable</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'I have very low emotional resilience'}</t>
+          <t>I am very valuable</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_very_valuable'}</t>
+          <t>i_am_somewhat_valuable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'I am very valuable'}</t>
+          <t>I am somewhat valuable</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_somewhat_valuable'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'I am somewhat valuable'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>i_am_somewhat_worthless</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>I am somewhat worthless</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_somewhat_worthless'}</t>
+          <t>i_am_worthless</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'I am somewhat worthless'}</t>
+          <t>I am worthless</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>self_worth_choices</t>
+          <t>self_worth_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_worthless'}</t>
+          <t>i_am_very_valuable</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'I am worthless'}</t>
+          <t>I am very valuable</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_very_valuable'}</t>
+          <t>somewhat_valuable</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'I am very valuable'}</t>
+          <t>Somewhat valuable</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_valuable'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat valuable'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_worthless</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat worthless</t>
         </is>
       </c>
     </row>
@@ -1879,29 +1879,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_worthless'}</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat worthless'}</t>
+          <t>Worthless</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>self_worth_2_choices</t>
+          <t>self_description_4_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'worthless'}</t>
+          <t>i_am_a_very_confident_person</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Worthless'}</t>
+          <t>I am a very confident person</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_confident_person'}</t>
+          <t>i_am_a_somewhat_confident_person</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very confident person'}</t>
+          <t>I am a somewhat confident person</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_confident_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat confident person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_uncertain_person</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat uncertain person</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_uncertain_person'}</t>
+          <t>i_am_an_uncertain_person</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat uncertain person'}</t>
+          <t>I am an uncertain person</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>self_description_4_choices</t>
+          <t>self_description_5_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_an_uncertain_person'}</t>
+          <t>i_am_a_very_self-assured_person</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'I am an uncertain person'}</t>
+          <t>I am a very self-assured person</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_self-assured_person'}</t>
+          <t>i_am_a_somewhat_self-assured_person</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very self-assured person'}</t>
+          <t>I am a somewhat self-assured person</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_self-assured_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat self-assured person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_uncertain_person</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat uncertain person</t>
         </is>
       </c>
     </row>
@@ -2049,29 +2049,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_uncertain_person'}</t>
+          <t>i_am_an_uncertain_person</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat uncertain person'}</t>
+          <t>I am an uncertain person</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>self_description_5_choices</t>
+          <t>self_description_6_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_an_uncertain_person'}</t>
+          <t>very_young</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'I am an uncertain person'}</t>
+          <t>Very young</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'very_young'}</t>
+          <t>somewhat_young</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Very young'}</t>
+          <t>Somewhat young</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_young'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat young'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_old</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat old</t>
         </is>
       </c>
     </row>
@@ -2134,29 +2134,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_old'}</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat old'}</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>self_description_6_choices</t>
+          <t>self_description_7_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'old'}</t>
+          <t>i_am_a_very_resilient_person</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Old'}</t>
+          <t>I am a very resilient person</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_resilient_person'}</t>
+          <t>i_am_a_somewhat_resilient_person</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very resilient person'}</t>
+          <t>I am a somewhat resilient person</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_resilient_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat resilient person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_fragile_person</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat fragile person</t>
         </is>
       </c>
     </row>
@@ -2219,29 +2219,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_fragile_person'}</t>
+          <t>i_am_a_fragile_person</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat fragile person'}</t>
+          <t>I am a fragile person</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>self_description_7_choices</t>
+          <t>self_description_8_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_fragile_person'}</t>
+          <t>i_am_a_very_valuable_person</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'I am a fragile person'}</t>
+          <t>I am a very valuable person</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_valuable_person'}</t>
+          <t>i_am_a_somewhat_valuable_person</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very valuable person'}</t>
+          <t>I am a somewhat valuable person</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_valuable_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat valuable person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_worthless_person</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat worthless person</t>
         </is>
       </c>
     </row>
@@ -2304,29 +2304,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_worthless_person'}</t>
+          <t>i_am_a_worthless_person</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat worthless person'}</t>
+          <t>I am a worthless person</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>self_description_8_choices</t>
+          <t>self_description_9_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_worthless_person'}</t>
+          <t>very_old</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'I am a worthless person'}</t>
+          <t>Very old</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'very_old'}</t>
+          <t>somewhat_old</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Very old'}</t>
+          <t>Somewhat old</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_old'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat old'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>somewhat_young</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Somewhat young</t>
         </is>
       </c>
     </row>
@@ -2389,29 +2389,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_young'}</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat young'}</t>
+          <t>Young</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>self_description_9_choices</t>
+          <t>self_description_10_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_'young'}</t>
+          <t>i_am_a_very_fragile_person</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': 'Young'}</t>
+          <t>I am a very fragile person</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_fragile_person'}</t>
+          <t>i_am_a_somewhat_fragile_person</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very fragile person'}</t>
+          <t>I am a somewhat fragile person</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_fragile_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat fragile person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_resilient_person</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat resilient person</t>
         </is>
       </c>
     </row>
@@ -2474,29 +2474,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_resilient_person'}</t>
+          <t>i_am_a_resilient_person</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat resilient person'}</t>
+          <t>I am a resilient person</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>self_description_10_choices</t>
+          <t>self_description_11_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_resilient_person'}</t>
+          <t>i_am_a_very_valuable_person</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 'I am a resilient person'}</t>
+          <t>I am a very valuable person</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_valuable_person'}</t>
+          <t>i_am_a_somewhat_valuable_person</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very valuable person'}</t>
+          <t>I am a somewhat valuable person</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_valuable_person'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat valuable person'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>i_am_a_somewhat_worthless_person</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>I am a somewhat worthless person</t>
         </is>
       </c>
     </row>
@@ -2559,29 +2559,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_worthless_person'}</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat worthless person'}</t>
+          <t>Worthless</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>self_description_11_choices</t>
+          <t>self_description_12_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_'worthless'}</t>
+          <t>i_am_a_very_old_person</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 'Worthless'}</t>
+          <t>I am a very old person</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_old_person'}</t>
+          <t>i_am_a_somewhat_old_person</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very old person'}</t>
+          <t>I am a somewhat old person</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_old_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat old person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_young_person</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat young person</t>
         </is>
       </c>
     </row>
@@ -2644,29 +2644,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_young_person'}</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat young person'}</t>
+          <t>Young</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>self_description_12_choices</t>
+          <t>self_description_13_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'label':_'young'}</t>
+          <t>i_am_a_very_old_person</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'label': 'Young'}</t>
+          <t>I am a very old person</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_old_person'}</t>
+          <t>i_am_a_somewhat_old_person</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very old person'}</t>
+          <t>I am a somewhat old person</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_old_person'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat old person'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>i_am_a_somewhat_young_person</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>I am a somewhat young person</t>
         </is>
       </c>
     </row>
@@ -2729,29 +2729,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_young_person'}</t>
+          <t>young</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat young person'}</t>
+          <t>Young</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>self_description_13_choices</t>
+          <t>self_worth_3_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'label':_'young'}</t>
+          <t>i_am_a_very_valuable_person</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'label': 'Young'}</t>
+          <t>I am a very valuable person</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_valuable_person'}</t>
+          <t>i_am_a_somewhat_valuable_person</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very valuable person'}</t>
+          <t>I am a somewhat valuable person</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_valuable_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat valuable person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_worthless_person</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat worthless person</t>
         </is>
       </c>
     </row>
@@ -2814,29 +2814,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_worthless_person'}</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat worthless person'}</t>
+          <t>Worthless</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>self_worth_3_choices</t>
+          <t>self_worth_4_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'label':_'worthless'}</t>
+          <t>i_am_very_valuable</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'label': 'Worthless'}</t>
+          <t>I am very valuable</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_very_valuable'}</t>
+          <t>somewhat_valuable</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'label': 'I am very valuable'}</t>
+          <t>Somewhat valuable</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_valuable'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat valuable'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>i_am_somewhat_worthless</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>I am somewhat worthless</t>
         </is>
       </c>
     </row>
@@ -2899,29 +2899,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_somewhat_worthless'}</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'label': 'I am somewhat worthless'}</t>
+          <t>Worthless</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>self_worth_4_choices</t>
+          <t>self_worth_5_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'label':_'worthless'}</t>
+          <t>i_am_a_very_valuable_person</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'label': 'Worthless'}</t>
+          <t>I am a very valuable person</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_very_valuable_person'}</t>
+          <t>i_am_a_somewhat_valuable_person</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'label': 'I am a very valuable person'}</t>
+          <t>I am a somewhat valuable person</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_valuable_person'}</t>
+          <t>i_am_a_neutral_person</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat valuable person'}</t>
+          <t>I am a neutral person</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_neutral_person'}</t>
+          <t>i_am_a_somewhat_worthless_person</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'label': 'I am a neutral person'}</t>
+          <t>I am a somewhat worthless person</t>
         </is>
       </c>
     </row>
@@ -2984,29 +2984,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_a_somewhat_worthless_person'}</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'label': 'I am a somewhat worthless person'}</t>
+          <t>Worthless</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>self_worth_5_choices</t>
+          <t>self_worth_6_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'label':_'worthless'}</t>
+          <t>i_am_very_valuable</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'label': 'Worthless'}</t>
+          <t>I am very valuable</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_very_valuable'}</t>
+          <t>somewhat_valuable</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'label': 'I am very valuable'}</t>
+          <t>Somewhat valuable</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_valuable'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat valuable'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>i_am_somewhat_worthless</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>I am somewhat worthless</t>
         </is>
       </c>
     </row>
@@ -3069,29 +3069,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_somewhat_worthless'}</t>
+          <t>worthless</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'label': 'I am somewhat worthless'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>self_worth_6_choices</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>{'label':_'worthless'}</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>{'label': 'Worthless'}</t>
+          <t>Worthless</t>
         </is>
       </c>
     </row>
